--- a/regressor_scores_mae.xlsx
+++ b/regressor_scores_mae.xlsx
@@ -474,7 +474,7 @@
         <v>0.378</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02</v>
+        <v>0.019</v>
       </c>
       <c r="F2" t="n">
         <v>0.048</v>
@@ -543,7 +543,7 @@
         <v>0.407</v>
       </c>
       <c r="E5" t="n">
-        <v>0.074</v>
+        <v>0.077</v>
       </c>
       <c r="F5" t="n">
         <v>0.058</v>
